--- a/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_predictions_scores.xlsx
+++ b/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_predictions_scores.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[["got-your-back/fmbox.py", "got-your-back/labellang.py"], ["got-your-back/gyb.py"]]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_predictions_scores.xlsx
+++ b/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_predictions_scores.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[["got-your-back/fmbox.py", "got-your-back/gyb.py"], ["got-your-back/labellang.py", "got-your-back/gyb.py"]]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_predictions_scores.xlsx
+++ b/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_predictions_scores.xlsx
@@ -1,37 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wiamlachqer/Library/Mobile Documents/com~apple~CloudDocs/Capstone/Multi-Agents-Systems-Benchmarking-for-Software-Engineering/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8C51C8-870D-764D-9E88-A1E289722DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+  <si>
+    <t>idx</t>
+  </si>
+  <si>
+    <t>dependency_groups</t>
+  </si>
+  <si>
+    <t>gt</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>[['got-your-back/gyb.py', 'got-your-back/fmbox.py'], ['got-your-back/gyb.py', 'got-your-back/labellang.py']]</t>
+  </si>
+  <si>
+    <t>[['got-your-back/labellang.py', 'got-your-back/gyb.py'], ['got-your-back/fmbox.py', 'got-your-back/gyb.py']]</t>
+  </si>
+  <si>
+    <t>[['SRCNN-pytorch/models.py', 'SRCNN-pytorch/train.py'], ['SRCNN-pytorch/datasets.py', 'SRCNN-pytorch/train.py'], ['SRCNN-pytorch/utils.py', 'SRCNN-pytorch/train.py'], ['SRCNN-pytorch/models.py', 'SRCNN-pytorch/test.py'], ['SRCNN-pytorch/utils.py', 'SRCNN-pytorch/test.py'], ['SRCNN-pytorch/prepare.py', 'SRCNN-pytorch/datasets.py']]</t>
+  </si>
+  <si>
+    <t>[['SRCNN-pytorch/utils.py', 'SRCNN-pytorch/train.py'], ['SRCNN-pytorch/models.py', 'SRCNN-pytorch/train.py'], ['SRCNN-pytorch/datasets.py', 'SRCNN-pytorch/train.py'], ['SRCNN-pytorch/utils.py', 'SRCNN-pytorch/test.py'], ['SRCNN-pytorch/models.py', 'SRCNN-pytorch/test.py'], ['SRCNN-pytorch/utils.py', 'SRCNN-pytorch/prepare.py']]</t>
+  </si>
+  <si>
+    <t>[['ConvLSTM-Pytorch/convlstm.py', 'ConvLSTM-Pytorch/convlstm_decoder.py']]</t>
+  </si>
+  <si>
+    <t>[["src/Socks5Server.php", "src/Protocol/Socks5Protocol.php"], ["src/Protocol/Socks5Protocol.php", "src/Auth/AuthenticationHandler.php"], ["src/Auth/AuthenticationHandler.php", "src/Config/ConfigLoader.php"], ["src/Socks5Server.php", "src/Connection/ConnectionManager.php"], ["src/Connection/ConnectionManager.php", "src/Protocol/Socks5Protocol.php"], ["bin/start.php", "src/Socks5Server.php"], ["bin/stop.php", "src/Socks5Server.php"], ["config/socks5.config.php", "src/Config/ConfigLoader.php"], ["src/Socks5Server.php", "src/Relay/DataRelay.php"], ["src/Relay/DataRelay.php", "src/Connection/ConnectionManager.php"]]</t>
+  </si>
+  <si>
+    <t>[['repos_otherLanguage/python\\php-socks5\\config.php', 'repos_otherLanguage/python\\php-socks5\\start.php']]</t>
+  </si>
+  <si>
+    <t>[['indrnn/ind_rnn_cell.py', 'indrnn/ind_rnn_cell_test.py'], ['indrnn/ind_rnn_cell.py', 'indrnn/examples/addition_rnn.py'], ['indrnn/ind_rnn_cell.py', 'indrnn/examples/sequential_mnist.py']]</t>
+  </si>
+  <si>
+    <t>[['indrnn/ind_rnn_cell.py', 'indrnn/examples/sequential_mnist.py'], ['indrnn/ind_rnn_cell.py', 'indrnn/examples/addition_rnn.py'], ['indrnn/ind_rnn_cell.py', 'indrnn/ind_rnn_cell_test.py']]</t>
+  </si>
+  <si>
+    <t>[["tesla-apiscraper/apiconfig.py", "tesla-apiscraper/teslajson.py"], ["tesla-apiscraper/teslajson.py", "tesla-apiscraper/apiscraper.py"], ["tesla-apiscraper/apiscraper.py", "tesla-apiscraper/srtmread.py"]]</t>
+  </si>
+  <si>
+    <t>[['tesla-apiscraper/teslajson.py', 'tesla-apiscraper/apiscraper.py'], ['tesla-apiscraper/apiconfig.py', 'tesla-apiscraper/teslajson.py', 'tesla-apiscraper/apiscraper.py'], ['tesla-apiscraper/srtmread.py', 'tesla-apiscraper/apiscraper.py']]</t>
+  </si>
+  <si>
+    <t>[['pytorch-made/made.py', 'pytorch-made/run.py']]</t>
+  </si>
+  <si>
+    <t>[['TradingView-data-scraper/app.py', 'TradingView-data-scraper/runp-heroku.py']]</t>
+  </si>
+  <si>
+    <t>[["rest-api-samples/python/move_datasource_server.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/move_workbook_server.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/move_workbook_projects.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/move_workbook_sites.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/publish_workbook.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/update_permission.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/user_permission_audit.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/users_by_group.py", "rest-api-samples/python/version.py"], ["rest-api-samples/python/webhooks.py", "rest-api-samples/python/version.py"]]</t>
+  </si>
+  <si>
+    <t>[['rest-api-samples/python/version.py', 'rest-api-samples/python/users_by_group.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/webhooks.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/publish_workbook.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/update_permission.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/move_workbook_sites.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/move_datasource_server.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/move_workbook_projects.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/user_permission_audit.py'], ['rest-api-samples/python/version.py', 'rest-api-samples/python/move_workbook_server.py']]</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[['Super-mario-bros-PPO-pytorch/src/env.py', 'Super-mario-bros-PPO-pytorch/src/process.py', 'Super-mario-bros-PPO-pytorch/train.py'], ['Super-mario-bros-PPO-pytorch/src/model.py', 'Super-mario-bros-PPO-pytorch/src/process.py', 'Super-mario-bros-PPO-pytorch/train.py'], ['Super-mario-bros-PPO-pytorch/src/model.py', 'Super-mario-bros-PPO-pytorch/test.py'], ['Super-mario-bros-PPO-pytorch/src/model.py', 'Super-mario-bros-PPO-pytorch/train.py'], ['Super-mario-bros-PPO-pytorch/src/env.py', 'Super-mario-bros-PPO-pytorch/test.py'], ['Super-mario-bros-PPO-pytorch/src/process.py', 'Super-mario-bros-PPO-pytorch/train.py'], ['Super-mario-bros-PPO-pytorch/src/env.py', 'Super-mario-bros-PPO-pytorch/train.py']]</t>
+  </si>
+  <si>
+    <t>[['horrifying-pdf-experiments/generate.py', 'horrifying-pdf-experiments/generate_breakout.py']]</t>
+  </si>
+  <si>
+    <t>[['CloudFail/cloudfail.py', 'CloudFail/DNSDumpsterAPI.py'], ['CloudFail/cloudfail.py', 'CloudFail/socks.py'], ['CloudFail/cloudfail.py', 'CloudFail/sockshandler.py'], ['CloudFail/sockshandler.py', 'CloudFail/socks.py'], ['CloudFail/DNSDumpsterAPI.py', 'CloudFail/sockshandler.py']]</t>
+  </si>
+  <si>
+    <t>[['CloudFail/DNSDumpsterAPI.py', 'CloudFail/cloudfail.py'], ['CloudFail/socks.py', 'CloudFail/sockshandler.py'], ['CloudFail/socks.py', 'CloudFail/cloudfail.py']]</t>
+  </si>
+  <si>
+    <t>[['Tiling/main.py', 'Tiling/tile.py']]</t>
+  </si>
+  <si>
+    <t>[['Tiling/tile.py', 'Tiling/main.py']]</t>
+  </si>
+  <si>
+    <t>[["Edu-Mail-Generator/bot.py", "Edu-Mail-Generator/helper.py"], ["Edu-Mail-Generator/bot.py", "Edu-Mail-Generator/__constants/const.py"], ["Edu-Mail-Generator/bot.py", "Edu-Mail-Generator/__colors__/colors.py"], ["Edu-Mail-Generator/setup.py", "Edu-Mail-Generator/__dwnldDrivers/versions.py"], ["Edu-Mail-Generator/helper.py", "Edu-Mail-Generator/__colors__/colors.py"], ["Edu-Mail-Generator/__banner/myBanner.py", "Edu-Mail-Generator/__colors__/colors.py"]]</t>
+  </si>
+  <si>
+    <t>[['Edu-Mail-Generator/__colors__/colors.py', 'Edu-Mail-Generator/bot.py'], ['Edu-Mail-Generator/helper.py', 'Edu-Mail-Generator/bot.py'], ['Edu-Mail-Generator/__dwnldDrivers/versions.py', 'Edu-Mail-Generator/setup.py'], ['Edu-Mail-Generator/__colors__/colors.py', 'Edu-Mail-Generator/helper.py', 'Edu-Mail-Generator/bot.py'], ['Edu-Mail-Generator/__banner/myBanner.py', 'Edu-Mail-Generator/bot.py'], ['Edu-Mail-Generator/__constants/const.py', 'Edu-Mail-Generator/bot.py']]</t>
+  </si>
+  <si>
+    <t>[['microsoft-teams-class-attender/bot.py', 'microsoft-teams-class-attender/discord_webhook.py']]</t>
+  </si>
+  <si>
+    <t>[['microsoft-teams-class-attender/discord_webhook.py', 'microsoft-teams-class-attender/bot.py']]</t>
+  </si>
+  <si>
+    <t>[['twitchchess/state.py', 'twitchchess/play.py'], ['twitchchess/generate_training_set.py', 'twitchchess/state.py'], ['twitchchess/train.py', 'twitchchess/generate_training_set.py'], ['twitchchess/play.py', 'twitchchess/train.py']]</t>
+  </si>
+  <si>
+    <t>[['twitchchess/state.py', 'twitchchess/generate_training_set.py'], ['twitchchess/train.py', 'twitchchess/play.py'], ['twitchchess/state.py', 'twitchchess/play.py']]</t>
+  </si>
+  <si>
+    <t>[['MapTilesDownloader/src/file_writer.py', 'MapTilesDownloader/src/mbtiles_writer.py'], ['MapTilesDownloader/src/mbtiles_writer.py', 'MapTilesDownloader/src/repo_writer.py'], ['MapTilesDownloader/src/repo_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/server.py', 'MapTilesDownloader/src/utils.py'], ['MapTilesDownloader/src/utils.py', 'MapTilesDownloader/src/file_writer.py']]</t>
+  </si>
+  <si>
+    <t>[['MapTilesDownloader/src/repo_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/file_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/utils.py', 'MapTilesDownloader/src/repo_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/mbtiles_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/mbtiles_writer.py', 'MapTilesDownloader/src/repo_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/utils.py', 'MapTilesDownloader/src/mbtiles_writer.py', 'MapTilesDownloader/src/repo_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/utils.py', 'MapTilesDownloader/src/mbtiles_writer.py', 'MapTilesDownloader/src/server.py'], ['MapTilesDownloader/src/utils.py', 'MapTilesDownloader/src/server.py']]</t>
+  </si>
+  <si>
+    <t>[['pytorch_memonger/test_memory_baseline.py', 'pytorch_memonger/models/baseline/densenet.py'], ['pytorch_memonger/test_memory_baseline.py', 'pytorch_memonger/models/baseline/resnet.py'], ['pytorch_memonger/test_memory_baseline.py', 'pytorch_memonger/models/baseline/vnet.py'], ['pytorch_memonger/test_memory_baseline.py', 'pytorch_memonger/models/baseline/word_language_model.py'], ['pytorch_memonger/test_memory_optimized.py', 'pytorch_memonger/models/optimized/densenet_new.py'], ['pytorch_memonger/test_memory_optimized.py', 'pytorch_memonger/models/optimized/resnet_new.py'], ['pytorch_memonger/test_memory_optimized.py', 'pytorch_memonger/models/optimized/vnet_new.py'], ['pytorch_memonger/test_memory_optimized.py', 'pytorch_memonger/models/optimized/word_language_model_new.py']]</t>
+  </si>
+  <si>
+    <t>[['pytorch_memonger/models/baseline/word_language_model.py', 'pytorch_memonger/test_memory_baseline.py'], ['pytorch_memonger/models/optimized/word_language_model_new.py', 'pytorch_memonger/test_memory_optimized.py'], ['pytorch_memonger/models/baseline/resnet.py', 'pytorch_memonger/test_memory_baseline.py'], ['pytorch_memonger/models/baseline/vnet.py', 'pytorch_memonger/test_memory_baseline.py'], ['pytorch_memonger/models/optimized/vnet_new.py', 'pytorch_memonger/test_memory_optimized.py'], ['pytorch_memonger/models/baseline/densenet.py', 'pytorch_memonger/test_memory_baseline.py'], ['pytorch_memonger/models/optimized/resnet_new.py', 'pytorch_memonger/test_memory_optimized.py'], ['pytorch_memonger/models/optimized/densenet_new.py', 'pytorch_memonger/test_memory_optimized.py']]</t>
+  </si>
+  <si>
+    <t>[['document-scanner/rect.py', 'document-scanner/scanner.py']]</t>
+  </si>
+  <si>
+    <t>[['R-BERT/main.py', 'R-BERT/trainer.py'], ['R-BERT/trainer.py', 'R-BERT/model.py'], ['R-BERT/trainer.py', 'R-BERT/data_loader.py'], ['R-BERT/trainer.py', 'R-BERT/utils.py'], ['R-BERT/main.py', 'R-BERT/data_loader.py'], ['R-BERT/main.py', 'R-BERT/utils.py'], ['R-BERT/predict.py', 'R-BERT/model.py'], ['R-BERT/predict.py', 'R-BERT/utils.py'], ['R-BERT/trainer.py', 'R-BERT/official_eval.py'], ['R-BERT/model.py', 'R-BERT/utils.py']]</t>
+  </si>
+  <si>
+    <t>[['R-BERT/model.py', 'R-BERT/trainer.py', 'R-BERT/main.py'], ['R-BERT/official_eval.py', 'R-BERT/utils.py', 'R-BERT/predict.py'], ['R-BERT/utils.py', 'R-BERT/data_loader.py', 'R-BERT/main.py'], ['R-BERT/trainer.py', 'R-BERT/main.py'], ['R-BERT/utils.py', 'R-BERT/main.py'], ['R-BERT/official_eval.py', 'R-BERT/utils.py', 'R-BERT/main.py'], ['R-BERT/model.py', 'R-BERT/predict.py'], ['R-BERT/utils.py', 'R-BERT/predict.py'], ['R-BERT/official_eval.py', 'R-BERT/utils.py', 'R-BERT/data_loader.py', 'R-BERT/main.py'], ['R-BERT/data_loader.py', 'R-BERT/main.py'], ['R-BERT/utils.py', 'R-BERT/trainer.py', 'R-BERT/main.py'], ['R-BERT/official_eval.py', 'R-BERT/utils.py', 'R-BERT/trainer.py', 'R-BERT/main.py']]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +174,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,52 +498,306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>idx</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>dependency_groups</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>gt</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[["got-your-back/fmbox.py", "got-your-back/gyb.py"], ["got-your-back/labellang.py", "got-your-back/gyb.py"]]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[['got-your-back/labellang.py', 'got-your-back/gyb.py'], ['got-your-back/fmbox.py', 'got-your-back/gyb.py']]</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>0.85833333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>0.71666666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>0.3928571428571429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18">
+        <v>0.43333333333333329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
